--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -744,24 +744,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,16 +1182,16 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -1264,15 +1264,15 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1328,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1474,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1614,22 +1614,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,33 +1757,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1903,33 +1903,33 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1939,19 +1939,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2012,19 +2012,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2127,20 +2127,20 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
@@ -2158,19 +2158,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2523,19 +2523,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2669,19 +2669,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2715,16 +2715,16 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2749,12 +2749,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2815,19 +2815,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2895,12 +2895,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2961,19 +2961,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3107,19 +3107,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3153,24 +3153,24 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,20 +3217,20 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3239,11 +3239,11 @@
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3301,9 +3301,9 @@
       <c r="I39" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3545,19 +3545,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3731,17 +3731,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3883,24 +3883,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4169,17 +4169,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4248,24 +4248,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4388,17 +4388,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,33 +4458,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4540,24 +4540,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4604,33 +4604,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4680,17 +4680,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4750,33 +4750,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4823,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
-        </is>
-      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,20 +5042,20 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5064,11 +5064,11 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -5206,15 +5206,15 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,0%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5347,20 +5347,20 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5629,17 +5629,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>21</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5781,24 +5781,24 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5848,22 +5848,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5927,11 +5927,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6027,19 +6027,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6104,8 +6104,446 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -665,22 +665,22 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -884,17 +884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,24 +963,24 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,14 +997,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1027,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1111,9 +1111,9 @@
       <c r="I9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1143,14 +1143,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1173,25 +1173,25 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,14 +1216,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1249,17 +1249,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1289,14 +1289,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,14 +1362,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>▲ 58,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,14 +1435,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,14 +1508,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,3%</t>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,14 +1581,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,14 +1654,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>▲ 152,6%</t>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,14 +1727,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1766,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,14 +1800,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1906,17 +1906,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,14 +1946,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1979,17 +1979,17 @@
           <t>R$ 57,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,14 +2019,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2049,33 +2049,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,14 +2092,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,14 +2165,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2195,33 +2195,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,14 +2238,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,14 +2311,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2377,21 +2377,21 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2450,21 +2450,21 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2530,14 +2530,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2669,21 +2669,21 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2711,20 +2711,20 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2749,14 +2749,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2788,24 +2788,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,14 +2822,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,14 +2895,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2934,11 +2934,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2968,14 +2968,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,14 +3041,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3074,17 +3074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3107,21 +3107,21 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3149,20 +3149,20 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,14 +3187,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 297,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,14 +3260,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3299,24 +3299,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3333,14 +3333,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3406,14 +3406,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3445,11 +3445,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,14 +3479,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3512,22 +3512,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3545,21 +3545,21 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3591,11 +3591,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3625,14 +3625,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3691,21 +3691,21 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3771,14 +3771,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3801,33 +3801,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,14 +3844,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3917,14 +3917,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4063,14 +4063,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4096,22 +4096,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4136,14 +4136,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4169,17 +4169,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,14 +4209,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,14 +4282,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4312,33 +4312,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4355,14 +4355,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4394,24 +4394,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,14 +4428,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,24 +4467,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,14 +4501,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4540,11 +4540,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4574,14 +4574,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,14 +4647,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4686,11 +4686,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4720,14 +4720,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4753,17 +4753,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,14 +4793,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4826,17 +4826,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4866,14 +4866,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4969,33 +4969,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,14 +5012,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5051,16 +5051,16 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,14 +5085,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5115,33 +5115,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,14 +5158,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5193,20 +5193,20 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
@@ -5231,14 +5231,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5261,33 +5261,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,14 +5304,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       <c r="I67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,14 +5377,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,14 +5450,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5489,11 +5489,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5523,14 +5523,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,14 +5596,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5629,17 +5629,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5669,14 +5669,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,14 +5742,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5772,33 +5772,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,14 +5815,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,14 +5888,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5927,24 +5927,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,14 +5961,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,14 +6034,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6107,14 +6107,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6137,33 +6137,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,14 +6180,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6219,11 +6219,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,14 +6253,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6286,22 +6286,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
@@ -6326,14 +6326,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6365,11 +6365,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6399,14 +6399,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6429,33 +6429,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6465,21 +6465,21 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6542,8 +6542,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -698,19 +698,19 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,33 +808,33 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -844,19 +844,19 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,33 +954,33 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -990,19 +990,19 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1100,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1173,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1216,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1246,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1289,12 +1289,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1328,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1362,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1392,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1435,12 +1435,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1538,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1611,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1684,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1766,16 +1766,16 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1800,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1830,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 152,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1912,11 +1912,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1946,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1976,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2052,17 +2052,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2092,12 +2092,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2122,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>▲ 96,6%</t>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2198,22 +2198,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>10</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,33 +2268,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2341,33 +2341,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2414,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2487,33 +2487,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,3%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2523,19 +2523,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2560,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,6%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2633,33 +2633,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,1%</t>
+        <v>20</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2669,19 +2669,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2711,20 +2711,20 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>8</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
@@ -2742,19 +2742,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2779,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 183,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2852,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2888,19 +2888,19 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2925,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2961,19 +2961,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +2998,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 115,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3071,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>19</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3107,19 +3107,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3153,16 +3153,16 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3217,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3253,19 +3253,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3299,16 +3299,16 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
@@ -3333,12 +3333,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3363,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3399,19 +3399,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3439,17 +3439,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3509,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3545,19 +3545,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3582,33 +3582,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3655,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3691,19 +3691,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3737,24 +3737,24 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,20 +3801,20 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3823,11 +3823,11 @@
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3885,9 +3885,9 @@
       <c r="I47" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3947,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4029,11 +4029,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4063,12 +4063,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4093,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4129,19 +4129,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4175,11 +4175,11 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,33 +4239,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4315,17 +4315,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4385,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4467,24 +4467,24 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4531,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4613,11 +4613,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4677,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4720,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4753,17 +4753,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,12 +4793,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4832,24 +4832,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,33 +4896,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4972,17 +4972,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5042,33 +5042,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5124,24 +5124,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5188,33 +5188,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5264,17 +5264,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5304,12 +5304,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5334,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5377,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5407,33 +5407,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5480,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
-        </is>
-      </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,33 +5553,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5648,11 +5648,11 @@
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5699,33 +5699,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5742,12 +5742,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
@@ -5790,15 +5790,15 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5845,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5929,22 +5929,22 @@
       <c r="I75" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5961,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5991,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6073,11 +6073,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,33 +6137,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6213,17 +6213,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6253,12 +6253,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6283,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6365,24 +6365,24 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6432,22 +6432,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
@@ -6472,12 +6472,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6511,11 +6511,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,33 +6575,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6611,19 +6611,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6657,11 +6657,11 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6688,8 +6688,446 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -819,9 +823,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,55 +958,59 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1044,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,33 +1108,33 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,19 +1144,19 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1182,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1246,33 +1254,33 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1282,19 +1290,19 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1328,11 +1336,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1362,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1392,33 +1400,33 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1428,19 +1436,19 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1468,17 +1476,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1508,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1538,33 +1546,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1581,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1611,33 +1619,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1654,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1684,33 +1692,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1727,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1757,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1766,24 +1774,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1800,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1830,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1873,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1906,17 +1914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1946,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1976,33 +1984,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2019,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2049,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2092,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2122,33 +2130,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2165,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2204,16 +2212,16 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2221,7 +2229,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2238,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2268,12 +2276,12 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -2286,15 +2294,15 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2311,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2350,11 +2358,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2384,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2414,33 +2422,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2457,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2496,11 +2504,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2530,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2560,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2603,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2636,22 +2644,22 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
@@ -2659,7 +2667,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2676,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2706,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2749,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2779,33 +2787,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2822,12 +2830,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2852,33 +2860,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2895,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2925,33 +2933,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>17</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -2961,19 +2969,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2998,33 +3006,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3034,19 +3042,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3071,33 +3079,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3107,19 +3115,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3149,20 +3157,20 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
@@ -3180,19 +3188,19 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3217,33 +3225,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3260,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3290,33 +3298,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3326,19 +3334,19 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3363,33 +3371,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3399,19 +3407,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3436,33 +3444,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>12</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3479,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3509,33 +3517,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3545,19 +3553,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3591,16 +3599,16 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
@@ -3608,7 +3616,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3625,12 +3633,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3655,33 +3663,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>34</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3691,19 +3699,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3737,16 +3745,16 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3771,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3801,33 +3809,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3837,19 +3845,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3877,17 +3885,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3917,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3947,33 +3955,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3983,19 +3991,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4020,33 +4028,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4063,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4093,33 +4101,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>6</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4129,19 +4137,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4166,7 +4174,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4175,24 +4183,24 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4209,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4239,20 +4247,20 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>16</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4261,11 +4269,11 @@
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4282,12 +4290,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4323,9 +4331,9 @@
       <c r="I53" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4355,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4385,33 +4393,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4428,12 +4436,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4467,11 +4475,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4501,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4531,33 +4539,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>15</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4567,19 +4575,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4613,11 +4621,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4647,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4677,33 +4685,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>8</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4720,12 +4728,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4753,17 +4761,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4793,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4823,33 +4831,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4866,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4896,7 +4904,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4905,24 +4913,24 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4939,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4969,33 +4977,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5012,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5051,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5085,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5115,33 +5123,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5158,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5191,17 +5199,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5231,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5261,7 +5269,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5270,24 +5278,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>18,2%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5304,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5334,33 +5342,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5377,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5410,17 +5418,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5450,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5480,33 +5488,33 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5523,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5553,7 +5561,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5562,24 +5570,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5596,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5626,33 +5634,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5669,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5702,17 +5710,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5742,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5772,33 +5780,33 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>9</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5815,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5845,33 +5853,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5888,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5918,33 +5926,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5961,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5991,33 +5999,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>10</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6034,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6064,20 +6072,20 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6086,11 +6094,11 @@
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6107,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6137,33 +6145,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6180,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6210,12 +6218,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -6228,15 +6236,15 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6253,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6283,33 +6291,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,0%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6326,12 +6334,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6356,7 +6364,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6369,20 +6377,20 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6399,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6429,33 +6437,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6472,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6511,11 +6519,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6545,12 +6553,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6575,33 +6583,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6618,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6651,17 +6659,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6691,12 +6699,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6721,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>21</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6764,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6794,7 +6802,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6803,24 +6811,24 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6837,12 +6845,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6870,22 +6878,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+        <v>25</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -6910,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6949,11 +6957,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6983,12 +6991,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7013,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7049,19 +7057,19 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7095,11 +7103,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7126,8 +7134,446 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -748,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -812,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,8 +816,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -830,37 +828,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -896,9 +896,9 @@
       <c r="I6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,14 +928,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -958,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -966,10 +966,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -978,41 +976,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1044,11 +1040,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,14 +1074,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1108,7 +1104,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1112,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,39 +1124,41 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1265,9 +1265,9 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1297,12 +1297,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1338,9 +1338,9 @@
       <c r="I12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1370,14 +1370,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1403,17 +1403,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1443,14 +1443,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1482,11 +1482,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,14 +1516,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1546,33 +1546,33 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1582,21 +1582,21 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1662,14 +1662,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1695,22 +1695,22 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1735,12 +1735,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1776,9 +1776,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1808,14 +1808,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1838,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1881,14 +1881,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1914,17 +1914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,14 +1954,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1993,24 +1993,24 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2027,14 +2027,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2057,33 +2057,33 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2141,9 +2141,9 @@
       <c r="I23" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2173,14 +2173,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2203,25 +2203,25 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,14 +2246,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2279,17 +2279,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2319,14 +2319,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2358,24 +2358,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,14 +2392,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2422,33 +2422,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>▲ 58,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2465,14 +2465,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2498,17 +2498,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2538,14 +2538,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2568,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,3%</t>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2611,14 +2611,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2641,33 +2641,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,14 +2684,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2714,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>▲ 152,6%</t>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,14 +2757,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2796,24 +2796,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2830,14 +2830,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2860,33 +2860,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,14 +2903,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2936,17 +2936,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,14 +2976,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3009,17 +3009,17 @@
           <t>R$ 57,00</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,14 +3049,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3079,33 +3079,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,14 +3122,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3152,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3195,14 +3195,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3225,33 +3225,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3268,14 +3268,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3298,33 +3298,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,14 +3341,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3371,33 +3371,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3407,21 +3407,21 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3444,33 +3444,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3480,21 +3480,21 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3517,33 +3517,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,14 +3560,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3590,33 +3590,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3633,14 +3633,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3663,33 +3663,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3699,21 +3699,21 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3741,20 +3741,20 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
@@ -3779,14 +3779,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3818,24 +3818,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3852,14 +3852,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3882,33 +3882,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3925,14 +3925,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3964,11 +3964,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -3998,14 +3998,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4028,33 +4028,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4071,14 +4071,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4104,17 +4104,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4137,21 +4137,21 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4179,20 +4179,20 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,14 +4217,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4247,33 +4247,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
         <is>
-          <t>▲ 297,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,14 +4290,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4329,24 +4329,24 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,14 +4363,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4393,33 +4393,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,14 +4436,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4475,11 +4475,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4509,14 +4509,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4542,22 +4542,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4575,21 +4575,21 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4621,11 +4621,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4655,14 +4655,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4685,33 +4685,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4721,21 +4721,21 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,14 +4801,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4831,33 +4831,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,14 +4874,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -4947,14 +4947,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4977,33 +4977,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5093,14 +5093,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5126,22 +5126,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,14 +5166,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5199,17 +5199,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5239,14 +5239,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5269,33 +5269,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,14 +5312,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5342,33 +5342,33 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5385,14 +5385,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5424,24 +5424,24 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,14 +5458,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5497,24 +5497,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5531,14 +5531,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5570,11 +5570,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5604,14 +5604,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5643,11 +5643,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,14 +5677,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5716,11 +5716,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5750,14 +5750,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5783,17 +5783,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5823,14 +5823,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5856,17 +5856,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,14 +5896,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5926,33 +5926,33 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5969,14 +5969,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5999,33 +5999,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6042,14 +6042,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6081,16 +6081,16 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6115,14 +6115,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6145,33 +6145,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6188,14 +6188,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6223,20 +6223,20 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
@@ -6261,14 +6261,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6291,33 +6291,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6334,14 +6334,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6375,22 +6375,22 @@
       <c r="I81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,14 +6407,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6437,33 +6437,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,14 +6480,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6519,11 +6519,11 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6553,14 +6553,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6583,33 +6583,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,14 +6626,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6659,17 +6659,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6699,14 +6699,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6729,33 +6729,33 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6772,14 +6772,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6802,33 +6802,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6845,14 +6845,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6875,33 +6875,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,14 +6918,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6957,24 +6957,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6991,14 +6991,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7021,33 +7021,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,14 +7064,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7103,11 +7103,11 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,14 +7137,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7167,33 +7167,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,14 +7210,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7249,11 +7249,11 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7283,14 +7283,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7316,22 +7316,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7356,14 +7356,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,14 +7429,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7459,33 +7459,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7495,21 +7495,21 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7541,11 +7541,11 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7572,8 +7572,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -625,19 +625,19 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -771,19 +771,19 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,51 +816,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -894,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -921,19 +917,19 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -967,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1040,11 +1036,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,12 +1147,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1186,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1297,12 +1293,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1336,11 +1332,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1370,12 +1366,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,7 +1396,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1408,47 +1404,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1482,11 +1482,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1516,12 +1516,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1628,11 +1628,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1692,33 +1692,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1728,19 +1728,19 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1774,11 +1774,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1838,33 +1838,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1874,19 +1874,19 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1920,11 +1920,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,33 +1984,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2060,17 +2060,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2130,33 +2130,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2203,33 +2203,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▲ 85,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2285,24 +2285,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2349,33 +2349,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2425,17 +2425,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,33 +2495,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>7,7%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2538,12 +2538,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2568,33 +2568,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,33 +2641,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2714,33 +2714,33 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2757,12 +2757,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2796,24 +2796,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2860,33 +2860,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,33 +3006,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,33 +3079,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,33 +3152,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>15</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3225,33 +3225,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,33 +3298,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3341,12 +3341,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3371,33 +3371,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3444,33 +3444,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3487,12 +3487,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3520,9 +3520,9 @@
           <t>R$ 36,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,3%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3553,19 +3553,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,33 +3590,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,6%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3626,19 +3626,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3663,33 +3663,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3699,19 +3699,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3736,33 +3736,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3772,19 +3772,19 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,33 +3809,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 183,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3845,19 +3845,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3882,33 +3882,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3955,33 +3955,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3991,19 +3991,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4028,33 +4028,33 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4110,24 +4110,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4179,20 +4179,20 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4250,17 +4250,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4283,19 +4283,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4320,33 +4320,33 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4363,12 +4363,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4393,33 +4393,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4429,19 +4429,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4466,33 +4466,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4539,33 +4539,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4621,24 +4621,24 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4685,33 +4685,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 131,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▼ 54,2%</t>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>16</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4721,19 +4721,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4767,11 +4767,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4831,33 +4831,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>14</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4913,11 +4913,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4977,33 +4977,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5013,19 +5013,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5059,11 +5059,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5093,12 +5093,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,33 +5123,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5239,12 +5239,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,33 +5269,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5345,17 +5345,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5385,12 +5385,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5415,33 +5415,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5497,24 +5497,24 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5531,12 +5531,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5561,33 +5561,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5637,17 +5637,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5716,24 +5716,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,12 +5750,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5793,20 +5793,20 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5862,11 +5862,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6002,17 +6002,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6072,33 +6072,33 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6154,24 +6154,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6188,12 +6188,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6218,33 +6218,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="3" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6369,20 +6369,20 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6446,24 +6446,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>10</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,12 +6480,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6510,20 +6510,20 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6532,11 +6532,11 @@
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,12 +6553,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6586,17 +6586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6665,24 +6665,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6738,24 +6738,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>11</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6805,17 +6805,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6878,17 +6878,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,0%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6957,24 +6957,24 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -6991,12 +6991,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7030,24 +7030,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,12 +7064,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7097,17 +7097,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7170,17 +7170,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7251,22 +7251,22 @@
       <c r="I93" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7318,20 +7318,20 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>25</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
@@ -7356,12 +7356,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7395,11 +7395,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7459,33 +7459,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7605,33 +7605,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>20</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7641,19 +7641,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7687,11 +7687,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7718,8 +7718,300 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,47 +670,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -735,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,47 +747,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,47 +824,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +902,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -963,7 +975,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -997,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1063,19 +1075,19 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1108,51 +1120,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1186,11 +1194,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1213,19 +1221,19 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1259,11 +1267,11 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1293,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1326,17 +1334,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1359,19 +1367,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1396,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1404,51 +1412,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1473,7 +1477,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1484,22 +1488,22 @@
       <c r="I14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1509,19 +1513,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1555,7 +1559,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1589,12 +1593,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1630,9 +1634,9 @@
       <c r="I16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1655,19 +1659,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1703,7 +1707,7 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
@@ -1735,12 +1739,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1774,11 +1778,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1801,19 +1805,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1841,17 +1845,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1881,12 +1885,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1920,11 +1924,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1947,19 +1951,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1984,33 +1988,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2020,19 +2024,19 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2066,11 +2070,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2093,19 +2097,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2130,33 +2134,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2166,19 +2170,19 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2212,11 +2216,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2239,19 +2243,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2276,7 +2280,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2285,24 +2289,24 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2312,19 +2316,19 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2352,17 +2356,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2385,19 +2389,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2431,11 +2435,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2458,19 +2462,19 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2495,33 +2499,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2531,19 +2535,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2577,11 +2581,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2604,19 +2608,19 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2641,7 +2645,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2650,24 +2654,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2677,19 +2681,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2717,17 +2721,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2750,19 +2754,19 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2796,11 +2800,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2830,12 +2834,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2860,55 +2864,59 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>4</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2936,17 +2944,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2976,12 +2984,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3006,33 +3014,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3042,19 +3050,19 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3079,7 +3087,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3088,24 +3096,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3122,12 +3130,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3152,55 +3160,59 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>5</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3234,11 +3246,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>5</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3268,12 +3280,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3298,33 +3310,33 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3334,19 +3346,19 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3374,17 +3386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3414,12 +3426,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3444,33 +3456,33 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3480,19 +3492,19 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3517,33 +3529,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3560,12 +3572,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3590,33 +3602,33 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3626,19 +3638,19 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3663,33 +3675,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3706,12 +3718,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3736,33 +3748,33 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3779,12 +3791,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3809,33 +3821,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3845,19 +3857,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3882,33 +3894,33 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr">
-        <is>
-          <t>▲ 296,6%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L47" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3918,19 +3930,19 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3955,33 +3967,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,1%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -3991,19 +4003,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4028,25 +4040,25 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L49" s="2" t="n">
@@ -4054,7 +4066,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4064,19 +4076,19 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4101,33 +4113,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▲ 183,3%</t>
+        <v>13</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4144,12 +4156,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4174,7 +4186,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4183,7 +4195,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4192,15 +4204,15 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4210,19 +4222,19 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4247,33 +4259,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4290,12 +4302,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4323,17 +4335,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4356,19 +4368,19 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4393,7 +4405,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4402,24 +4414,24 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4436,12 +4448,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4466,33 +4478,33 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>15</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4502,19 +4514,19 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4542,17 +4554,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4575,19 +4587,19 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4612,33 +4624,33 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L57" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -4648,19 +4660,19 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4685,33 +4697,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="3" t="inlineStr">
         <is>
-          <t>▲ 297,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4721,19 +4733,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4758,33 +4770,33 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -4794,19 +4806,19 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4831,25 +4843,25 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>10</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
@@ -4857,7 +4869,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4867,19 +4879,19 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4904,33 +4916,33 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -4940,19 +4952,19 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4977,33 +4989,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>18</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5020,12 +5032,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5050,33 +5062,33 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5086,19 +5098,19 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5123,33 +5135,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>17</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5159,19 +5171,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5196,33 +5208,33 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5232,19 +5244,19 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5269,33 +5281,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5305,19 +5317,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5342,7 +5354,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5351,24 +5363,24 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5378,19 +5390,19 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5415,33 +5427,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5451,19 +5463,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5491,17 +5503,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5524,19 +5536,19 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5561,33 +5573,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5604,12 +5616,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5634,33 +5646,33 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 115,00</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -5677,12 +5689,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5707,33 +5719,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5750,12 +5762,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5780,25 +5792,25 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L73" s="2" t="n">
@@ -5823,12 +5835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5853,7 +5865,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5862,24 +5874,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -5889,19 +5901,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5926,7 +5938,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5935,24 +5947,24 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -5969,12 +5981,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6008,11 +6020,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6035,19 +6047,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6075,17 +6087,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6115,12 +6127,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6154,11 +6166,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6181,19 +6193,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6218,33 +6230,33 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H79" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6261,12 +6273,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6294,17 +6306,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H80" s="4" t="inlineStr">
+      <c r="H80" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6334,12 +6346,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6364,25 +6376,25 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L81" s="2" t="n">
@@ -6390,7 +6402,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6407,12 +6419,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6437,33 +6449,33 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6480,12 +6492,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6510,33 +6522,33 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -6553,12 +6565,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6583,33 +6595,33 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>14</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6626,12 +6638,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6656,7 +6668,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6665,24 +6677,24 @@
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -6699,12 +6711,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6729,25 +6741,25 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,4%</t>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -6755,7 +6767,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6765,19 +6777,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6811,11 +6823,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6845,12 +6857,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6875,33 +6887,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -6918,12 +6930,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6957,11 +6969,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6991,12 +7003,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7021,33 +7033,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7064,12 +7076,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7097,17 +7109,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7137,12 +7149,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7167,33 +7179,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7210,12 +7222,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7240,7 +7252,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7249,24 +7261,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7283,12 +7295,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7313,33 +7325,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7356,12 +7368,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7389,17 +7401,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7429,12 +7441,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7459,33 +7471,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7502,12 +7514,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7532,7 +7544,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7543,22 +7555,22 @@
       <c r="I97" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7575,12 +7587,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7605,33 +7617,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7648,12 +7660,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7687,11 +7699,11 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7721,12 +7733,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7751,33 +7763,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7794,12 +7806,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7835,9 +7847,9 @@
       <c r="I101" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7867,12 +7879,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7897,7 +7909,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7906,24 +7918,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7933,19 +7945,19 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -7973,17 +7985,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -8010,8 +8022,1760 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,14 +786,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -816,7 +816,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -824,10 +824,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -836,39 +834,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -940,12 +936,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1017,14 +1013,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1047,7 +1043,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1055,8 +1051,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1065,37 +1063,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,14 +1167,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1208,9 +1208,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1240,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,14 +1317,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1356,11 +1356,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1390,14 +1390,14 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1428,8 +1428,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1438,39 +1440,41 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1502,11 +1506,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1536,14 +1540,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1569,17 +1573,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1609,14 +1613,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1648,11 +1652,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,14 +1686,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1712,33 +1716,33 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1755,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1796,9 +1800,9 @@
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1828,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1858,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1867,7 +1871,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1876,15 +1880,15 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1901,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1940,11 +1944,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1974,14 +1978,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2007,17 +2011,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2047,14 +2051,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2086,11 +2090,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2120,14 +2124,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2150,33 +2154,33 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2193,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2232,11 +2236,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2266,14 +2270,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2296,7 +2300,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2305,7 +2309,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2314,15 +2318,15 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2339,14 +2343,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2378,7 +2382,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2412,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2485,12 +2489,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2558,12 +2562,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2631,14 +2635,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2661,7 +2665,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2669,10 +2673,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2681,41 +2683,39 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2741,17 +2741,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2781,14 +2781,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2819,8 +2819,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2829,39 +2831,41 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2884,33 +2888,33 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2927,14 +2931,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2957,7 +2961,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2965,10 +2969,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2977,41 +2979,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3052,15 +3052,15 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3227,12 +3227,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3304,14 +3304,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3343,11 +3343,11 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3377,14 +3377,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3415,8 +3415,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3425,39 +3427,41 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3489,11 +3493,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3523,14 +3527,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3556,17 +3560,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3596,12 +3600,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3639,7 +3643,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3669,14 +3673,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3699,33 +3703,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3742,14 +3746,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3772,7 +3776,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3780,10 +3784,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3792,41 +3794,39 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3857,10 +3857,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3869,39 +3867,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3973,14 +3969,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4003,7 +3999,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4011,8 +4007,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4021,39 +4019,41 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4084,8 +4084,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4094,39 +4096,41 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4160,9 +4164,9 @@
       <c r="I50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4192,14 +4196,14 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4233,9 +4237,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -4265,14 +4269,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4304,11 +4308,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4338,14 +4342,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4377,11 +4381,11 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4411,14 +4415,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4444,17 +4448,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4484,12 +4488,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4525,9 +4529,9 @@
       <c r="I55" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4557,14 +4561,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4587,33 +4591,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4630,14 +4634,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4669,11 +4673,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4703,14 +4707,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4733,7 +4737,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4742,24 +4746,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4776,14 +4780,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4815,11 +4819,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4849,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4888,11 +4892,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4922,14 +4926,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4961,11 +4965,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4995,14 +4999,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5034,11 +5038,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5068,14 +5072,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5107,11 +5111,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5141,14 +5145,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5180,11 +5184,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5214,14 +5218,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5253,11 +5257,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5287,14 +5291,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5326,11 +5330,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5360,14 +5364,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5399,11 +5403,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5433,14 +5437,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5472,11 +5476,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5506,14 +5510,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5545,11 +5549,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5579,14 +5583,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5618,11 +5622,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5652,14 +5656,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5691,11 +5695,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5725,14 +5729,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5764,11 +5768,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5798,14 +5802,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5837,11 +5841,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5871,14 +5875,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5910,11 +5914,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5937,21 +5941,21 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5974,7 +5978,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5982,10 +5986,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -5994,41 +5996,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6094,14 +6094,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6132,8 +6132,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6142,37 +6144,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6208,9 +6212,9 @@
       <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6240,14 +6244,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6270,7 +6274,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6278,10 +6282,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6290,41 +6292,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6356,11 +6356,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6390,14 +6390,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6428,8 +6428,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6438,39 +6440,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6502,11 +6506,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6536,14 +6540,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6577,9 +6581,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6609,12 +6613,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6650,9 +6654,9 @@
       <c r="I84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6682,14 +6686,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6715,17 +6719,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6755,14 +6759,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6794,11 +6798,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6828,14 +6832,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6858,33 +6862,33 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -6894,21 +6898,21 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6940,7 +6944,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -6974,14 +6978,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7007,22 +7011,22 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>7</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
@@ -7030,7 +7034,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7047,14 +7051,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7088,9 +7092,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7120,14 +7124,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7150,33 +7154,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 14,3%</t>
+        <v>14</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7193,14 +7197,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7226,17 +7230,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7266,14 +7270,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7296,7 +7300,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7305,24 +7309,24 @@
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7339,14 +7343,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7369,33 +7373,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7412,12 +7416,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7453,9 +7457,9 @@
       <c r="I95" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7485,14 +7489,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7515,25 +7519,25 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>▲ 600,0%</t>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
@@ -7541,7 +7545,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7558,14 +7562,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7591,17 +7595,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7631,14 +7635,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7661,7 +7665,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7670,24 +7674,24 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7704,14 +7708,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7734,33 +7738,33 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L99" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -7777,14 +7781,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7810,17 +7814,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7850,14 +7854,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7880,33 +7884,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 136,00</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7923,14 +7927,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7953,33 +7957,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -7996,14 +8000,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8026,33 +8030,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8069,14 +8073,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8099,7 +8103,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8108,24 +8112,24 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,9%</t>
+        <v>10</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8142,14 +8146,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8172,33 +8176,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8215,14 +8219,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8248,17 +8252,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,0%</t>
+        <v>18</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8288,14 +8292,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8321,17 +8325,17 @@
           <t>R$ 57,00</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8344,7 +8348,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8361,14 +8365,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8391,33 +8395,33 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8434,14 +8438,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8464,33 +8468,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>▲ 60,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8507,14 +8511,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8537,33 +8541,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J110" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8580,14 +8584,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8610,33 +8614,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8653,14 +8657,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8683,33 +8687,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,3%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8719,21 +8723,21 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8756,33 +8760,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,7%</t>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8792,21 +8796,21 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8829,33 +8833,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,1%</t>
+        <v>20</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8872,14 +8876,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8902,33 +8906,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+        <v>12</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8945,14 +8949,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8975,33 +8979,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 183,3%</t>
+        <v>19</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9011,21 +9015,21 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9053,20 +9057,20 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
@@ -9091,14 +9095,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9121,7 +9125,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9130,24 +9134,24 @@
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9164,14 +9168,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9194,33 +9198,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9237,14 +9241,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9276,11 +9280,11 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -9310,14 +9314,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9340,33 +9344,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9383,14 +9387,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9416,17 +9420,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9449,21 +9453,21 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9491,20 +9495,20 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
@@ -9512,7 +9516,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9529,14 +9533,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9559,33 +9563,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>6</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9602,14 +9606,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9632,7 +9636,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9641,24 +9645,24 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9675,14 +9679,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9705,33 +9709,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>16</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9748,14 +9752,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9787,11 +9791,11 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -9821,14 +9825,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9854,22 +9858,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>14</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
@@ -9877,7 +9881,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9887,21 +9891,21 @@
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9933,11 +9937,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9967,14 +9971,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9997,33 +10001,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10033,21 +10037,21 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10079,11 +10083,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10113,14 +10117,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10143,33 +10147,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10186,14 +10190,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10225,7 +10229,7 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10259,14 +10263,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10289,33 +10293,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10332,12 +10336,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10405,14 +10409,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10438,22 +10442,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>▼ 36,4%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
@@ -10461,7 +10465,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10478,14 +10482,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10511,17 +10515,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -10551,14 +10555,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10581,33 +10585,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10624,14 +10628,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10654,33 +10658,33 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L139" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -10697,14 +10701,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10727,7 +10731,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10736,24 +10740,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10770,14 +10774,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10800,7 +10804,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10809,24 +10813,24 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10843,14 +10847,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10882,11 +10886,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -10916,14 +10920,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10955,11 +10959,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,4%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10989,14 +10993,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11028,11 +11032,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11062,14 +11066,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11095,17 +11099,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11135,14 +11139,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11168,17 +11172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11208,14 +11212,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11238,33 +11242,33 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H147" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L147" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -11281,14 +11285,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11311,33 +11315,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11354,14 +11358,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11393,16 +11397,16 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
@@ -11410,7 +11414,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11427,14 +11431,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11457,33 +11461,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11500,14 +11504,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11535,20 +11539,20 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
@@ -11573,14 +11577,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11603,33 +11607,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11646,14 +11650,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11676,7 +11680,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11687,22 +11691,22 @@
       <c r="I153" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11719,14 +11723,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11749,33 +11753,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>11</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11792,14 +11796,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11831,11 +11835,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11865,14 +11869,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11895,33 +11899,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>13</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11938,14 +11942,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11971,17 +11975,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12011,14 +12015,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12041,33 +12045,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12084,14 +12088,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12114,33 +12118,33 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J159" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L159" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -12157,14 +12161,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12187,33 +12191,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>21</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12230,14 +12234,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12260,7 +12264,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12269,24 +12273,24 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12303,14 +12307,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12333,33 +12337,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>25</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12376,14 +12380,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12415,11 +12419,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12449,14 +12453,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12479,33 +12483,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>15</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12522,14 +12526,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12561,11 +12565,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12595,14 +12599,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12628,22 +12632,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 21,7%</t>
+        <v>20</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12668,14 +12672,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12707,11 +12711,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12741,14 +12745,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12771,33 +12775,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12807,85 +12811,231 @@
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-VM</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada vermelho</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>5336631388</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="n">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>Sem calcular</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,10 +597,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -609,41 +607,39 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -675,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -709,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -786,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -829,7 +825,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -936,14 +932,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -966,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -974,10 +970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -986,39 +980,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1090,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1167,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1197,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1205,8 +1197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1215,37 +1209,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1317,14 +1313,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1358,9 +1354,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1390,12 +1386,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1467,14 +1463,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1506,11 +1502,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1540,14 +1536,14 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1570,7 +1566,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1578,8 +1574,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1588,39 +1586,41 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1686,14 +1686,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1719,17 +1719,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1862,33 +1862,33 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,9 +1946,9 @@
       <c r="I20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,14 +1978,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2026,15 +2026,15 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2051,14 +2051,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2090,11 +2090,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2124,14 +2124,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2157,17 +2157,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2197,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2236,11 +2236,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2270,14 +2270,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2300,33 +2300,33 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2343,14 +2343,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,14 +2416,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2464,15 +2464,15 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2489,14 +2489,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2562,12 +2562,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2781,14 +2781,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2819,10 +2819,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2831,41 +2829,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2891,17 +2887,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2931,14 +2927,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2961,7 +2957,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2969,8 +2965,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2979,39 +2977,41 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3034,33 +3034,33 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3077,14 +3077,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3115,10 +3115,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3127,41 +3125,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3184,7 +3180,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3202,15 +3198,15 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3227,12 +3223,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3304,12 +3300,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3347,7 +3343,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -3377,12 +3373,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3454,14 +3450,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3493,11 +3489,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3527,14 +3523,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3557,7 +3553,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3565,8 +3561,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3575,39 +3573,41 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3639,11 +3639,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3673,14 +3673,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3706,17 +3706,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3849,33 +3849,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3892,14 +3892,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3930,10 +3930,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3942,41 +3940,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3999,7 +3995,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4007,10 +4003,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4019,39 +4013,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4123,14 +4115,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4153,7 +4145,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4161,8 +4153,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4171,39 +4165,41 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4226,7 +4222,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4234,8 +4230,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4244,39 +4242,41 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4310,9 +4310,9 @@
       <c r="I52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4342,14 +4342,14 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4383,9 +4383,9 @@
       <c r="I53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -4415,14 +4415,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4454,11 +4454,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4488,14 +4488,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4527,11 +4527,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4561,14 +4561,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4594,17 +4594,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4675,9 +4675,9 @@
       <c r="I57" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4707,14 +4707,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4737,33 +4737,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4780,14 +4780,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4819,11 +4819,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4853,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4892,24 +4892,24 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4926,14 +4926,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4965,11 +4965,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4999,14 +4999,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5038,11 +5038,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5072,14 +5072,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5111,11 +5111,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5145,14 +5145,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5218,14 +5218,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5257,11 +5257,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5291,14 +5291,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5330,11 +5330,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5364,14 +5364,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5403,11 +5403,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,14 +5437,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5476,11 +5476,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5510,14 +5510,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5549,11 +5549,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5622,11 +5622,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5656,14 +5656,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5695,11 +5695,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5729,14 +5729,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5768,11 +5768,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5802,14 +5802,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5841,11 +5841,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5875,14 +5875,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5914,11 +5914,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5948,14 +5948,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5987,11 +5987,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6021,14 +6021,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6087,21 +6087,21 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6132,10 +6132,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6144,41 +6142,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6210,11 +6206,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6244,14 +6240,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6274,7 +6270,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6282,8 +6278,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6292,37 +6290,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6358,9 +6358,9 @@
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6390,14 +6390,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6428,10 +6428,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6440,41 +6438,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6506,11 +6502,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6540,14 +6536,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6570,7 +6566,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6578,8 +6574,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6588,39 +6586,41 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6652,11 +6652,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6686,14 +6686,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6727,9 +6727,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6800,9 +6800,9 @@
       <c r="I86" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6832,14 +6832,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6865,17 +6865,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6905,14 +6905,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6944,11 +6944,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6978,14 +6978,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7008,33 +7008,33 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7044,21 +7044,21 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7124,14 +7124,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7157,22 +7157,22 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7197,14 +7197,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7238,9 +7238,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7270,14 +7270,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7300,33 +7300,33 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7343,14 +7343,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7376,17 +7376,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="3" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7416,14 +7416,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7455,24 +7455,24 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7489,14 +7489,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7519,33 +7519,33 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7603,9 +7603,9 @@
       <c r="I97" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7635,14 +7635,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7665,25 +7665,25 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7708,14 +7708,14 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7741,17 +7741,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7781,14 +7781,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7820,24 +7820,24 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7854,14 +7854,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7884,33 +7884,33 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>▲ 58,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7927,14 +7927,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7960,17 +7960,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8000,14 +8000,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8030,33 +8030,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,3%</t>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8073,14 +8073,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8103,33 +8103,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8146,14 +8146,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8176,33 +8176,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>▲ 152,6%</t>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8219,14 +8219,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8258,24 +8258,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8292,14 +8292,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8322,33 +8322,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8365,14 +8365,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8398,17 +8398,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8438,14 +8438,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8471,17 +8471,17 @@
           <t>R$ 57,00</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8511,14 +8511,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8541,33 +8541,33 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8584,14 +8584,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8614,33 +8614,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J111" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8657,14 +8657,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8687,33 +8687,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8730,14 +8730,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8760,33 +8760,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8803,14 +8803,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8833,33 +8833,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8869,21 +8869,21 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8906,33 +8906,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8942,21 +8942,21 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8979,33 +8979,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9022,14 +9022,14 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9052,33 +9052,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9095,14 +9095,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9125,33 +9125,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9161,21 +9161,21 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9203,20 +9203,20 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
@@ -9241,14 +9241,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9280,24 +9280,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9314,14 +9314,14 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9344,33 +9344,33 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J121" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9387,14 +9387,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9426,11 +9426,11 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9460,14 +9460,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9490,33 +9490,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9533,14 +9533,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9566,17 +9566,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9599,21 +9599,21 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9641,20 +9641,20 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9679,14 +9679,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9709,33 +9709,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>▲ 297,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J126" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9752,14 +9752,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9791,24 +9791,24 @@
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9825,14 +9825,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9855,33 +9855,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9898,14 +9898,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9937,11 +9937,11 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -9971,14 +9971,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10004,22 +10004,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10037,21 +10037,21 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10083,11 +10083,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10117,14 +10117,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10147,33 +10147,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10183,21 +10183,21 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10229,11 +10229,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10263,14 +10263,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10293,33 +10293,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10336,14 +10336,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10375,7 +10375,7 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10409,14 +10409,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10439,33 +10439,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10555,14 +10555,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10588,22 +10588,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10628,14 +10628,14 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10661,17 +10661,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10701,14 +10701,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10731,33 +10731,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10774,14 +10774,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10804,33 +10804,33 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L141" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -10847,14 +10847,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -10886,24 +10886,24 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10920,14 +10920,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10950,7 +10950,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -10959,24 +10959,24 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10993,14 +10993,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11032,11 +11032,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11066,14 +11066,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11105,11 +11105,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11139,14 +11139,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11178,11 +11178,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11212,14 +11212,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11245,17 +11245,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11285,14 +11285,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11318,17 +11318,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11358,14 +11358,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11388,33 +11388,33 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L149" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -11431,14 +11431,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11461,33 +11461,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11504,14 +11504,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11543,16 +11543,16 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11577,14 +11577,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11607,33 +11607,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11650,14 +11650,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11685,20 +11685,20 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
@@ -11723,14 +11723,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11753,33 +11753,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11796,14 +11796,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -11837,22 +11837,22 @@
       <c r="I155" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11869,14 +11869,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11899,33 +11899,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11942,14 +11942,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11981,11 +11981,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12015,14 +12015,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12045,33 +12045,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12088,14 +12088,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12121,17 +12121,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12161,14 +12161,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12191,33 +12191,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12234,14 +12234,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12264,33 +12264,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12307,14 +12307,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12337,33 +12337,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12380,14 +12380,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -12419,24 +12419,24 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12453,14 +12453,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12483,33 +12483,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12526,14 +12526,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12565,11 +12565,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12599,14 +12599,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12629,33 +12629,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12672,14 +12672,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12711,11 +12711,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12745,14 +12745,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12778,22 +12778,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
@@ -12818,14 +12818,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12857,11 +12857,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12891,14 +12891,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12921,33 +12921,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12957,85 +12957,231 @@
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-VM</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada vermelho</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>5336631388</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="n">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>Sem calcular</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -735,7 +735,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -743,10 +743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -755,41 +753,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -821,11 +817,11 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -855,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -975,7 +971,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1005,12 +1001,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1112,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1120,10 +1116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1132,39 +1126,37 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1236,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1313,14 +1305,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1343,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1351,8 +1343,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1361,37 +1355,39 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1504,9 +1500,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1652,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1686,14 +1682,14 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1716,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1724,8 +1720,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1734,39 +1732,41 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1865,17 +1865,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1905,14 +1905,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -1944,11 +1944,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,14 +1978,14 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2008,33 +2008,33 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2092,9 +2092,9 @@
       <c r="I22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2124,14 +2124,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2172,15 +2172,15 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2197,14 +2197,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2236,11 +2236,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2270,14 +2270,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2303,17 +2303,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2343,14 +2343,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,14 +2416,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2446,33 +2446,33 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2489,14 +2489,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2528,11 +2528,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2562,14 +2562,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2610,15 +2610,15 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2635,14 +2635,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2927,14 +2927,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2965,10 +2965,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -2977,41 +2975,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3037,17 +3033,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3077,14 +3073,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3107,7 +3103,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3115,8 +3111,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3125,39 +3123,41 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3180,33 +3180,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3223,14 +3223,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3261,10 +3261,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3273,41 +3271,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3330,7 +3326,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3348,15 +3344,15 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3373,12 +3369,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3450,12 +3446,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3493,7 +3489,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3523,12 +3519,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3600,14 +3596,14 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3639,11 +3635,11 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3673,14 +3669,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3703,7 +3699,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3711,8 +3707,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>0</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3721,39 +3719,41 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3785,11 +3785,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3819,14 +3819,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3852,17 +3852,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -3965,14 +3965,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -3995,33 +3995,33 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4038,14 +4038,14 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4076,10 +4076,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4088,41 +4086,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4145,7 +4141,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4153,10 +4149,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4165,39 +4159,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4269,14 +4261,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4299,7 +4291,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4307,8 +4299,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4317,39 +4311,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4372,7 +4368,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4380,8 +4376,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4390,39 +4388,41 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4456,9 +4456,9 @@
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4488,14 +4488,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4529,9 +4529,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4561,14 +4561,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4600,11 +4600,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4634,14 +4634,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4673,11 +4673,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4707,14 +4707,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4740,17 +4740,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4780,12 +4780,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4821,9 +4821,9 @@
       <c r="I59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4853,14 +4853,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4883,33 +4883,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4926,14 +4926,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -4965,11 +4965,11 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -4999,14 +4999,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5038,24 +5038,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5072,14 +5072,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5111,11 +5111,11 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -5145,14 +5145,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5218,14 +5218,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5257,11 +5257,11 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5291,14 +5291,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5330,11 +5330,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5364,14 +5364,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5403,11 +5403,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,14 +5437,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5476,11 +5476,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5510,14 +5510,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5549,11 +5549,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5622,11 +5622,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5656,14 +5656,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5695,11 +5695,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5729,14 +5729,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5768,11 +5768,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5802,14 +5802,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5841,11 +5841,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5875,14 +5875,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5914,11 +5914,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5948,14 +5948,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -5987,11 +5987,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6021,14 +6021,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6060,11 +6060,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6094,14 +6094,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6133,11 +6133,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6167,14 +6167,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6206,11 +6206,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6233,21 +6233,21 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6278,10 +6278,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6290,41 +6288,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6356,11 +6352,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6390,14 +6386,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6420,7 +6416,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6428,8 +6424,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6438,37 +6436,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6504,9 +6504,9 @@
       <c r="I82" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6536,14 +6536,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6574,10 +6574,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6586,41 +6584,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6652,11 +6648,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▲ 25,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6686,14 +6682,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6716,7 +6712,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6724,8 +6720,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6734,39 +6732,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6798,11 +6798,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6832,14 +6832,14 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -6873,9 +6873,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6905,12 +6905,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6946,9 +6946,9 @@
       <c r="I88" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6978,14 +6978,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7011,17 +7011,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H89" s="4" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7051,14 +7051,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7090,11 +7090,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7124,14 +7124,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7154,33 +7154,33 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L91" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7190,21 +7190,21 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7270,14 +7270,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7303,22 +7303,22 @@
           <t>R$ 72,00</t>
         </is>
       </c>
-      <c r="H93" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>▲ 133,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L93" s="2" t="n">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7343,14 +7343,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7384,9 +7384,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7416,14 +7416,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7446,33 +7446,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7489,14 +7489,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7522,17 +7522,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H96" s="4" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7562,14 +7562,14 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7601,24 +7601,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7635,14 +7635,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7665,33 +7665,33 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7749,9 +7749,9 @@
       <c r="I99" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 53,3%</t>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7781,14 +7781,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7811,25 +7811,25 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7854,14 +7854,14 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7887,17 +7887,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7927,14 +7927,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7966,24 +7966,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8000,14 +8000,14 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
-        </is>
-      </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8030,33 +8030,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>▲ 58,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8073,14 +8073,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8106,17 +8106,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8146,14 +8146,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8176,33 +8176,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,3%</t>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8219,14 +8219,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8249,33 +8249,33 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8292,14 +8292,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8322,33 +8322,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 86,00</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>▲ 152,6%</t>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8365,14 +8365,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8404,24 +8404,24 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8438,14 +8438,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8468,33 +8468,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8511,14 +8511,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8544,17 +8544,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8584,14 +8584,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8617,17 +8617,17 @@
           <t>R$ 57,00</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>▲ 96,6%</t>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8657,14 +8657,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8687,33 +8687,33 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L112" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -8730,14 +8730,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8760,33 +8760,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8803,14 +8803,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8833,33 +8833,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▲ 30,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8876,14 +8876,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8906,33 +8906,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>▼ 58,3%</t>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8949,14 +8949,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -8979,33 +8979,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▲ 5,3%</t>
+        <v>26</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9015,21 +9015,21 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9052,33 +9052,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>▲ 296,6%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L117" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9088,21 +9088,21 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9125,33 +9125,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9168,14 +9168,14 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9198,33 +9198,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>▲ 62,5%</t>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9241,14 +9241,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9271,33 +9271,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▲ 183,3%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9307,21 +9307,21 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9349,20 +9349,20 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>13</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
@@ -9387,14 +9387,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9426,24 +9426,24 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>34</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9460,14 +9460,14 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9490,33 +9490,33 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 29,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -9533,14 +9533,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9572,11 +9572,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9606,14 +9606,14 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9636,33 +9636,33 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>8</v>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -9679,14 +9679,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9712,17 +9712,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>▼ 62,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9745,21 +9745,21 @@
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9787,20 +9787,20 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
@@ -9808,7 +9808,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9825,14 +9825,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9855,33 +9855,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>▲ 297,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9898,14 +9898,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -9928,7 +9928,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -9937,24 +9937,24 @@
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -9971,14 +9971,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10001,33 +10001,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▼ 6,7%</t>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10044,14 +10044,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10083,11 +10083,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10117,14 +10117,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10150,22 +10150,22 @@
           <t>R$ 33,00</t>
         </is>
       </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>▲ 87,5%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10183,21 +10183,21 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10229,11 +10229,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J133" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10263,14 +10263,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10293,33 +10293,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 33,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>15</v>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10329,21 +10329,21 @@
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10375,11 +10375,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10409,14 +10409,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10439,33 +10439,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10482,14 +10482,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10521,7 +10521,7 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10555,14 +10555,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10585,33 +10585,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10628,12 +10628,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10701,14 +10701,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10734,22 +10734,22 @@
           <t>R$ 108,00</t>
         </is>
       </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 49,8%</t>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>14</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10774,14 +10774,14 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10807,17 +10807,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10847,14 +10847,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10877,33 +10877,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
-        </is>
-      </c>
-      <c r="H142" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 3200,0%</t>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10920,14 +10920,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -10950,33 +10950,33 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L143" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -10993,14 +10993,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 215,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11032,24 +11032,24 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11066,14 +11066,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11096,7 +11096,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11105,24 +11105,24 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11139,14 +11139,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11178,11 +11178,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11212,14 +11212,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11251,11 +11251,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>2</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11285,14 +11285,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11324,11 +11324,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11358,14 +11358,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11391,17 +11391,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>▲ 350,0%</t>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11431,14 +11431,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11464,17 +11464,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11504,14 +11504,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11534,33 +11534,33 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
-        </is>
-      </c>
-      <c r="H151" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L151" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -11577,14 +11577,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11607,33 +11607,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>▼ 9,1%</t>
+        <v>2</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11650,14 +11650,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11689,16 +11689,16 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11723,14 +11723,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11753,33 +11753,33 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H154" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>10</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11796,14 +11796,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11831,20 +11831,20 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L155" s="2" t="n">
@@ -11869,14 +11869,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11899,33 +11899,33 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -11942,14 +11942,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11983,22 +11983,22 @@
       <c r="I157" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12015,14 +12015,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12045,33 +12045,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H158" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>▲ 8,3%</t>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12088,14 +12088,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12127,11 +12127,11 @@
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12161,14 +12161,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12191,33 +12191,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12234,14 +12234,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12267,17 +12267,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12307,14 +12307,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12337,33 +12337,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12380,14 +12380,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12410,33 +12410,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12453,14 +12453,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12483,33 +12483,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12526,14 +12526,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12565,24 +12565,24 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -12599,14 +12599,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12629,33 +12629,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H166" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12672,14 +12672,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12711,11 +12711,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12745,14 +12745,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12775,33 +12775,33 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
-        </is>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>▲ 11,1%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -12818,14 +12818,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12857,11 +12857,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12891,14 +12891,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -12924,22 +12924,22 @@
           <t>R$ 34,00</t>
         </is>
       </c>
-      <c r="H170" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J170" s="4" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▲ 11,1%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
@@ -12964,14 +12964,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -13003,11 +13003,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13037,14 +13037,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-095-VM</t>
@@ -13067,33 +13067,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
-        </is>
-      </c>
-      <c r="H172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>18</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13103,85 +13103,231 @@
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-VM</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada vermelho</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>5336631388</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="n">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>Sem calcular</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
+++ b/saida_skus/SKU_UTD-095-VM-SECA-SALADA-VERMELHO.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -673,9 +673,9 @@
       <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -684,11 +684,11 @@
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -811,17 +811,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -889,10 +889,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -901,39 +899,37 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -958,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -971,20 +967,20 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1001,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1031,7 +1027,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1039,51 +1035,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1117,7 +1109,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1151,12 +1143,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1189,51 +1181,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1258,7 +1246,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1266,51 +1254,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1335,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1343,10 +1327,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1355,39 +1337,37 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1392,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,51 +1400,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,7 +1465,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1497,8 +1473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1507,37 +1485,39 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1562,7 +1542,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1570,51 +1550,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,7 +1615,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1647,47 +1623,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1712,7 +1692,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1720,10 +1700,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I17" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1732,39 +1710,37 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,7 +1765,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,47 +1773,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1862,7 +1842,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1870,8 +1850,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1880,37 +1862,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1935,7 +1919,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1943,47 +1927,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2008,55 +1996,59 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2090,11 +2082,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2124,12 +2116,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2154,7 +2146,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2162,8 +2154,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>2</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2172,37 +2166,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2236,11 +2232,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2270,12 +2266,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2308,8 +2304,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2318,37 +2316,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2449,17 +2449,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2528,11 +2528,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2592,33 +2592,33 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2674,11 +2674,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2756,15 +2756,15 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L31" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2820,11 +2820,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2854,12 +2854,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3000,12 +3000,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3033,17 +3033,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3111,51 +3111,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3180,33 +3176,33 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3223,12 +3219,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3262,7 +3258,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3296,12 +3292,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3326,7 +3322,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3335,24 +3331,24 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3369,12 +3365,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3399,7 +3395,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3407,10 +3403,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3419,39 +3413,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3485,11 +3477,11 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -3519,12 +3511,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3549,7 +3541,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3557,10 +3549,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3569,39 +3559,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3635,7 +3623,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3669,12 +3657,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3746,12 +3734,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3779,9 +3767,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3819,12 +3807,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3892,12 +3880,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3922,7 +3910,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3931,24 +3919,24 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -3965,12 +3953,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3995,55 +3983,59 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4077,11 +4069,11 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -4111,12 +4103,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4141,7 +4133,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4149,8 +4141,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>1</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4159,37 +4153,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4214,7 +4210,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4222,10 +4218,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4234,39 +4228,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4338,12 +4330,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4368,7 +4360,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4376,51 +4368,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4488,12 +4476,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4527,11 +4515,11 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4561,12 +4549,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4594,9 +4582,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -4634,12 +4622,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4673,11 +4661,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4707,12 +4695,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4737,7 +4725,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4755,15 +4743,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4780,12 +4768,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4810,7 +4798,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4818,47 +4806,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4883,55 +4875,59 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4956,7 +4952,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -4964,47 +4960,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5038,24 +5038,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5184,11 +5184,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5330,11 +5330,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5437,12 +5437,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5470,17 +5470,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5549,11 +5549,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5583,12 +5583,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5622,24 +5622,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5697,9 +5697,9 @@
       <c r="I71" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5768,11 +5768,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5841,11 +5841,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5914,11 +5914,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5948,12 +5948,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5987,11 +5987,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6021,12 +6021,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -6094,12 +6094,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6133,11 +6133,11 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6206,11 +6206,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6279,11 +6279,11 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6354,9 +6354,9 @@
       <c r="I80" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6379,19 +6379,19 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6424,10 +6424,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6436,39 +6434,37 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6502,11 +6498,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6529,19 +6525,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6577,9 +6573,9 @@
       <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -6609,12 +6605,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6648,11 +6644,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6675,19 +6671,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6712,7 +6708,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6720,51 +6716,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6798,11 +6790,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6825,19 +6817,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6871,7 +6863,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6905,12 +6897,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6944,11 +6936,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -6978,12 +6970,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7008,7 +7000,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7016,47 +7008,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7090,11 +7086,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7124,12 +7120,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7157,17 +7153,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -7197,12 +7193,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7238,9 +7234,9 @@
       <c r="I92" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7270,12 +7266,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7300,55 +7296,59 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7382,11 +7382,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7446,33 +7446,33 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>▲ 133,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -7482,19 +7482,19 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7528,11 +7528,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7601,24 +7601,24 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>▼ 14,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -7628,19 +7628,19 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7668,17 +7668,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7741,17 +7741,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7774,19 +7774,19 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7811,33 +7811,33 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 85,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -7897,20 +7897,20 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>▼ 53,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -7927,12 +7927,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -7966,24 +7966,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8030,33 +8030,33 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>▲ 15,4%</t>
+          <t>▲ 133,3%</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8073,12 +8073,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8112,11 +8112,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8176,33 +8176,33 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 136,00</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>▲ 58,1%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>▼ 7,1%</t>
+          <t>▼ 14,3%</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L105" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8258,11 +8258,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8322,33 +8322,33 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 86,00</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>7</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L107" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8395,25 +8395,25 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>13</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 85,7%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L108" s="2" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8468,33 +8468,33 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 152,6%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J109" s="4" t="inlineStr">
-        <is>
-          <t>▲ 15,4%</t>
+        <v>7</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 53,3%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L109" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8550,24 +8550,24 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J110" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,9%</t>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -8584,12 +8584,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8614,33 +8614,33 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>15</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8690,17 +8690,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>▼ 15,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8760,33 +8760,33 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 136,00</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>▲ 96,6%</t>
+          <t>▲ 58,1%</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>▲ 62,5%</t>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,1%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="L113" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -8803,12 +8803,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8833,33 +8833,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -8906,33 +8906,33 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 86,00</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,3%</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>▲ 60,0%</t>
+        <v>14</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
+        <is>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L115" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -8979,33 +8979,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
-        <is>
-          <t>▲ 30,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9052,33 +9052,33 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 152,6%</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>▲ 15,4%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 58,3%</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9095,12 +9095,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9125,33 +9125,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>▲ 5,3%</t>
+          <t>▲ 5,9%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9161,19 +9161,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9198,33 +9198,33 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 115,00</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>▲ 296,6%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>▼ 7,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L119" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9234,19 +9234,19 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9271,33 +9271,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 144,00</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>▼ 44,1%</t>
+          <t>▼ 15,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9307,19 +9307,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>▲ 96,6%</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
@@ -9362,15 +9362,15 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -9380,19 +9380,19 @@
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9417,33 +9417,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="J122" s="4" t="inlineStr">
-        <is>
-          <t>▲ 183,3%</t>
+        <v>20</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9460,12 +9460,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9501,9 +9501,9 @@
       <c r="I123" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>▲ 60,0%</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -9526,19 +9526,19 @@
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9563,33 +9563,33 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 72,00</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 30,0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9645,11 +9645,11 @@
         </is>
       </c>
       <c r="I125" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>▲ 14,3%</t>
+        <v>5</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>▼ 58,3%</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -9672,19 +9672,19 @@
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9709,33 +9709,33 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 36,00</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>20</v>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>▲ 5,3%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="L126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -9745,19 +9745,19 @@
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9782,33 +9782,33 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 29,00</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 115,00</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>▲ 296,6%</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J127" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>▼ 7,7%</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L127" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -9825,12 +9825,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -9855,33 +9855,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 144,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>▼ 62,5%</t>
+          <t>▼ 44,1%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -9933,20 +9933,20 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 62,5%</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="L129" s="2" t="n">
@@ -9971,12 +9971,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10001,33 +10001,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 131,00</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>▲ 297,0%</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="J130" s="4" t="inlineStr">
         <is>
-          <t>▲ 14,3%</t>
+          <t>▲ 183,3%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10037,19 +10037,19 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10083,24 +10083,24 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L131" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10117,12 +10117,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10147,33 +10147,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 6,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10183,19 +10183,19 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10223,17 +10223,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10263,12 +10263,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10293,33 +10293,33 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 33,00</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 54,2%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>▲ 87,5%</t>
+        <v>3</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10366,33 +10366,33 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L135" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10439,33 +10439,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 72,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 62,5%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10482,12 +10482,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 29,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10521,24 +10521,24 @@
         </is>
       </c>
       <c r="I137" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L137" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10585,33 +10585,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 131,00</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 297,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>16</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▲ 14,3%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10628,12 +10628,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10667,11 +10667,11 @@
         </is>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10744,20 +10744,20 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 6,7%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10813,11 +10813,11 @@
         </is>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -10877,33 +10877,33 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 108,00</t>
+          <t>R$ 33,00</t>
         </is>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>▼ 49,8%</t>
+          <t>▼ 54,2%</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 36,4%</t>
+        <v>15</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 87,5%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -10913,19 +10913,19 @@
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Média</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -10953,17 +10953,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -10993,12 +10993,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 215,00</t>
+          <t>R$ 72,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11032,24 +11032,24 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 3200,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11066,12 +11066,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 36,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11105,24 +11105,24 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L145" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11172,17 +11172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11251,11 +11251,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11315,33 +11315,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 108,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11358,12 +11358,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11397,11 +11397,11 @@
         </is>
       </c>
       <c r="I149" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>▼ 44,4%</t>
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -11431,12 +11431,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11461,33 +11461,33 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 108,00</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 49,8%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>21</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 36,4%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11504,12 +11504,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11543,11 +11543,11 @@
         </is>
       </c>
       <c r="I151" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>▲ 350,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11577,12 +11577,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11607,33 +11607,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 215,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>33</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>▲ 3200,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11680,25 +11680,25 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 36,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L153" s="2" t="n">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -11723,12 +11723,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11762,24 +11762,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>▼ 9,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -11848,11 +11848,11 @@
         </is>
       </c>
       <c r="L155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -11902,17 +11902,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -11942,12 +11942,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 32,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -11983,22 +11983,22 @@
       <c r="I157" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 44,4%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L157" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12015,12 +12015,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12054,24 +12054,24 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 15,4%</t>
+        <v>6</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12088,12 +12088,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12121,17 +12121,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>▲ 66,7%</t>
+          <t>▲ 350,0%</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12200,11 +12200,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 8,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12264,33 +12264,33 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L161" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -12307,12 +12307,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12346,16 +12346,16 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 9,1%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12380,12 +12380,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12410,33 +12410,33 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H163" s="3" t="inlineStr">
+          <t>R$ 32,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
         </is>
       </c>
-      <c r="I163" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
       <c r="L163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -12453,12 +12453,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12492,11 +12492,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12526,12 +12526,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 32,00</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -12567,9 +12567,9 @@
       <c r="I165" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>▲ 25,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12638,16 +12638,16 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 66,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 15,4%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
@@ -12655,7 +12655,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12672,12 +12672,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12711,11 +12711,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12784,11 +12784,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 8,3%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -12818,12 +12818,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -12857,11 +12857,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -12921,33 +12921,33 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 68,00</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>▲ 11,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="L170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -12964,12 +12964,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -12997,17 +12997,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13037,12 +13037,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13067,33 +13067,33 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>R$ 34,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>▼ 21,7%</t>
+          <t>▼ 16,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L172" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -13151,22 +13151,22 @@
       <c r="I173" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="L173" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>R$ 68,00</t>
+          <t>R$ 34,00</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -13222,24 +13222,24 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>25</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 66,7%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="L174" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -13249,85 +13249,669 @@
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>Média</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J176" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>▲ 11,1%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 34,00</t>
+        </is>
+      </c>
+      <c r="H180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 21,7%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>5336631388</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-095-VM</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Seca salada vermelho</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>3771555819</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 68,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>8,7%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-095-VM</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Seca salada vermelho</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>5336631388</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 35,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 35,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>Sem calcular</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>